--- a/rtos-api-analysis/results/runtime/tizenrt_elapsed_time_summary.xlsx
+++ b/rtos-api-analysis/results/runtime/tizenrt_elapsed_time_summary.xlsx
@@ -492,25 +492,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>134886.9316770186</v>
+        <v>132571.9378881988</v>
       </c>
       <c r="C2" t="n">
-        <v>893.2909382584016</v>
+        <v>872.1838018960445</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>3394.762351143755</v>
+        <v>3323.691732929948</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>25666</v>
+        <v>27428</v>
       </c>
       <c r="H2" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I2" t="n">
         <v>162</v>
@@ -519,7 +519,7 @@
         <v>11</v>
       </c>
       <c r="K2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/rtos-api-analysis/results/runtime/tizenrt_elapsed_time_summary.xlsx
+++ b/rtos-api-analysis/results/runtime/tizenrt_elapsed_time_summary.xlsx
@@ -492,34 +492,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>132571.9378881988</v>
+        <v>295067.950310559</v>
       </c>
       <c r="C2" t="n">
-        <v>872.1838018960445</v>
+        <v>1916.025651367266</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>3323.691732929948</v>
+        <v>10187.23113497785</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>27428</v>
+        <v>112158</v>
       </c>
       <c r="H2" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I2" t="n">
         <v>162</v>
       </c>
       <c r="J2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/rtos-api-analysis/results/runtime/tizenrt_elapsed_time_summary.xlsx
+++ b/rtos-api-analysis/results/runtime/tizenrt_elapsed_time_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,52 +436,77 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>SourceTable</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Total(s)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Mean(s)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Median(s)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Median(min)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Standard Deviation(s)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Minimum(s)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Maximum(s)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Completed API Count</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>All API Count</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>&gt; 1-Hour</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>&gt; 30-Minutes</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>StoppedByMaxTime_yes</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>StoppedByMaxTime_no</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>StoppedByMaxTime_unknown</t>
         </is>
       </c>
     </row>
@@ -491,35 +516,52 @@
           <t>tizenrt</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>295067.950310559</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>walltime</t>
+        </is>
       </c>
       <c r="C2" t="n">
-        <v>1916.025651367266</v>
+        <v>465020.4106000001</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>2888.325531677019</v>
       </c>
       <c r="E2" t="n">
-        <v>10187.23113497785</v>
+        <v>0.0495</v>
       </c>
       <c r="F2" t="n">
+        <v>0.000825</v>
+      </c>
+      <c r="G2" t="n">
+        <v>9726.287576935196</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="I2" t="n">
+        <v>56929.8752</v>
+      </c>
+      <c r="J2" t="n">
+        <v>161</v>
+      </c>
+      <c r="K2" t="n">
+        <v>161</v>
+      </c>
+      <c r="L2" t="n">
+        <v>16</v>
+      </c>
+      <c r="M2" t="n">
+        <v>17</v>
+      </c>
+      <c r="N2" t="n">
         <v>0</v>
       </c>
-      <c r="G2" t="n">
-        <v>112158</v>
-      </c>
-      <c r="H2" t="n">
-        <v>154</v>
-      </c>
-      <c r="I2" t="n">
-        <v>162</v>
-      </c>
-      <c r="J2" t="n">
-        <v>14</v>
-      </c>
-      <c r="K2" t="n">
-        <v>14</v>
+      <c r="O2" t="n">
+        <v>161</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
